--- a/data/trans_orig/P19F$mañana-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016</t>
+          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016 (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76768</t>
+          <t>75682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105808</t>
+          <t>104805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>53084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>75738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134609</t>
+          <t>136588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175702</t>
+          <t>171916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71921</t>
+          <t>73228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55371</t>
+          <t>55933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>84934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120244</t>
+          <t>119542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139133</t>
+          <t>138272</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>165099</t>
+          <t>164575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83317</t>
+          <t>83935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104392</t>
+          <t>103327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>227769</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>263354</t>
+          <t>262614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>58029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83830</t>
+          <t>85166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68267</t>
+          <t>67780</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96190</t>
+          <t>95464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131178</t>
+          <t>134530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171048</t>
+          <t>172575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>53138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78613</t>
+          <t>78758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56711</t>
+          <t>56269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83333</t>
+          <t>82192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117491</t>
+          <t>117611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155618</t>
+          <t>154128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122838</t>
+          <t>122229</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146126</t>
+          <t>146584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120074</t>
+          <t>120459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>144376</t>
+          <t>143554</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>250455</t>
+          <t>252386</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>284880</t>
+          <t>285310</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,56%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99323</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132043</t>
+          <t>131131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137348</t>
+          <t>136312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176071</t>
+          <t>173693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>71797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102685</t>
+          <t>101978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85368</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123157</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>204402</t>
+          <t>207132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>233181</t>
+          <t>234011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57881</t>
+          <t>59068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69614</t>
+          <t>70281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>270112</t>
+          <t>271106</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>300031</t>
+          <t>298959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222923</t>
+          <t>221299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274228</t>
+          <t>269573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183816</t>
+          <t>183313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>223176</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416524</t>
+          <t>416657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>482842</t>
+          <t>480240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166801</t>
+          <t>167179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212494</t>
+          <t>213796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120413</t>
+          <t>119345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157300</t>
+          <t>156660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297839</t>
+          <t>293675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357238</t>
+          <t>357849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>456722</t>
+          <t>455805</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>498804</t>
+          <t>498674</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>325037</t>
+          <t>325934</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>357184</t>
+          <t>356665</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>792869</t>
+          <t>793960</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>848322</t>
+          <t>850631</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118991</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154758</t>
+          <t>154382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146846</t>
+          <t>145396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188450</t>
+          <t>186899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>277000</t>
+          <t>275005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330445</t>
+          <t>331373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80890</t>
+          <t>81542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114134</t>
+          <t>114077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105285</t>
+          <t>106197</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141227</t>
+          <t>142958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195604</t>
+          <t>195825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>243427</t>
+          <t>244590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>255383</t>
+          <t>253198</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>284361</t>
+          <t>283228</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>321633</t>
+          <t>319265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>351111</t>
+          <t>350661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>581800</t>
+          <t>584638</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>625976</t>
+          <t>627505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55650</t>
+          <t>56134</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82205</t>
+          <t>81470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>197271</t>
+          <t>199185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245849</t>
+          <t>248223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265158</t>
+          <t>265098</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>319265</t>
+          <t>317735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63345</t>
+          <t>62059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144114</t>
+          <t>142677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186128</t>
+          <t>186187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>190474</t>
+          <t>188247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>240041</t>
+          <t>237875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>112268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>133813</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>411977</t>
+          <t>412071</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>448943</t>
+          <t>448893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>533544</t>
+          <t>535955</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>575204</t>
+          <t>575336</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>687172</t>
+          <t>676341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>768663</t>
+          <t>764389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>732841</t>
+          <t>737572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>817245</t>
+          <t>822636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1451649</t>
+          <t>1447136</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1568367</t>
+          <t>1560745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507738</t>
+          <t>507483</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585875</t>
+          <t>589165</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>520730</t>
+          <t>522352</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>595212</t>
+          <t>598564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1047161</t>
+          <t>1050727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1159030</t>
+          <t>1157572</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1344536</t>
+          <t>1346041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1414871</t>
+          <t>1418057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1368820</t>
+          <t>1373333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1435967</t>
+          <t>1436181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2736572</t>
+          <t>2735160</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2835057</t>
+          <t>2832589</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>77160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104805</t>
+          <t>104998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>53120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75738</t>
+          <t>75760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136588</t>
+          <t>136648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171916</t>
+          <t>174192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>45676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73228</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35382</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55933</t>
+          <t>55428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84934</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119542</t>
+          <t>119813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>138272</t>
+          <t>140357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164575</t>
+          <t>164160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83935</t>
+          <t>83793</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103327</t>
+          <t>104047</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>229997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262614</t>
+          <t>262826</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58029</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85166</t>
+          <t>84505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67780</t>
+          <t>67320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95464</t>
+          <t>95382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134530</t>
+          <t>134509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172575</t>
+          <t>171341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78758</t>
+          <t>79139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56269</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82192</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117611</t>
+          <t>118175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154128</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122229</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146584</t>
+          <t>146790</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120459</t>
+          <t>119954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143554</t>
+          <t>145536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252386</t>
+          <t>249325</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>285310</t>
+          <t>284562</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98423</t>
+          <t>98630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131131</t>
+          <t>131477</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136312</t>
+          <t>135220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173693</t>
+          <t>173851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71797</t>
+          <t>71227</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101978</t>
+          <t>102397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>88974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121731</t>
+          <t>123937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>207132</t>
+          <t>207637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>234011</t>
+          <t>235171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70281</t>
+          <t>69580</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>271106</t>
+          <t>269738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>298959</t>
+          <t>299732</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221299</t>
+          <t>218527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269573</t>
+          <t>268588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183313</t>
+          <t>180196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>222309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416657</t>
+          <t>416212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480240</t>
+          <t>482810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167179</t>
+          <t>164381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213796</t>
+          <t>211462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119345</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156660</t>
+          <t>155759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293675</t>
+          <t>298926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357849</t>
+          <t>359164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>455805</t>
+          <t>456030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>498674</t>
+          <t>499639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>325934</t>
+          <t>324290</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>356665</t>
+          <t>356045</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>793960</t>
+          <t>791674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>850631</t>
+          <t>845714</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117014</t>
+          <t>119797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154382</t>
+          <t>155069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145396</t>
+          <t>145649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186899</t>
+          <t>185997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>275005</t>
+          <t>275928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331373</t>
+          <t>328732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81542</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114077</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106197</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142958</t>
+          <t>144593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,47 +2265,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>220996</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>194613</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>247288</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>29,79%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>26,23%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>35,31%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>220996</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>195825</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>244590</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>26,4%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>253198</t>
+          <t>254412</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>283228</t>
+          <t>283425</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>319265</t>
+          <t>321312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>350661</t>
+          <t>352407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>584638</t>
+          <t>583216</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>627505</t>
+          <t>627406</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,19 +2413,19 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>55615</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>80647</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>199185</t>
+          <t>200552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>248223</t>
+          <t>245543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265098</t>
+          <t>265337</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>317735</t>
+          <t>317934</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>38922</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>142677</t>
+          <t>144261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186187</t>
+          <t>187071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188247</t>
+          <t>189678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237875</t>
+          <t>240674</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>112268</t>
+          <t>113131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133813</t>
+          <t>133462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>412071</t>
+          <t>412809</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>448893</t>
+          <t>449872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>535955</t>
+          <t>534169</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>575336</t>
+          <t>576797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>676341</t>
+          <t>682735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>764389</t>
+          <t>771532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>737572</t>
+          <t>736693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>822636</t>
+          <t>822285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1447136</t>
+          <t>1443439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1560745</t>
+          <t>1567144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507483</t>
+          <t>507409</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>589165</t>
+          <t>588280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>522352</t>
+          <t>515998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>598564</t>
+          <t>597846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1050727</t>
+          <t>1051174</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1157572</t>
+          <t>1164640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1346041</t>
+          <t>1345232</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1418057</t>
+          <t>1417642</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1373333</t>
+          <t>1371645</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1436181</t>
+          <t>1438387</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2735160</t>
+          <t>2736150</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2832589</t>
+          <t>2835286</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Clase-trans_orig.xlsx
@@ -828,112 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>142</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57556</t>
+          <t>152504</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45676</t>
+          <t>140357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71323</t>
+          <t>164160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44820</t>
+          <t>94656</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>83793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55428</t>
+          <t>104047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>233</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>102376</t>
+          <t>247160</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>229997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>262826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>152504</t>
+          <t>57556</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>140357</t>
+          <t>45676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164160</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>44820</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83793</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104047</t>
+          <t>55428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>247160</t>
+          <t>102376</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229997</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>262826</t>
+          <t>119813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -1171,112 +1171,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65555</t>
+          <t>135551</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52912</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79139</t>
+          <t>146790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>133060</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55977</t>
+          <t>119954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83973</t>
+          <t>145536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134985</t>
+          <t>268611</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118175</t>
+          <t>249325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153501</t>
+          <t>284562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -1284,112 +1284,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135551</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122745</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146790</t>
+          <t>79139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133060</t>
+          <t>69430</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119954</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145536</t>
+          <t>83973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>128</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>268611</t>
+          <t>134985</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>249325</t>
+          <t>118175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>284562</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -1514,112 +1514,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>215</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86519</t>
+          <t>221065</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71227</t>
+          <t>207637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102397</t>
+          <t>235171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>65348</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>69580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>104498</t>
+          <t>286413</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>269738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123937</t>
+          <t>299732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -1627,112 +1627,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>221065</t>
+          <t>86519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>207637</t>
+          <t>71227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235171</t>
+          <t>102397</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65348</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57496</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69580</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>102</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>104498</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269738</t>
+          <t>88974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>299732</t>
+          <t>123937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -1857,112 +1857,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>460</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>189360</t>
+          <t>479054</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164381</t>
+          <t>456030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211462</t>
+          <t>499639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>328</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>137270</t>
+          <t>341996</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118339</t>
+          <t>324290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155759</t>
+          <t>356045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>788</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326630</t>
+          <t>821050</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>298926</t>
+          <t>791674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359164</t>
+          <t>845714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -1970,112 +1970,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>479054</t>
+          <t>189360</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>456030</t>
+          <t>164381</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>499639</t>
+          <t>211462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>341996</t>
+          <t>137270</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>324290</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>356045</t>
+          <t>155759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>821050</t>
+          <t>326630</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>791674</t>
+          <t>298926</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>845714</t>
+          <t>359164</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -2200,112 +2200,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96888</t>
+          <t>269931</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80109</t>
+          <t>254412</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>283425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>324</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124108</t>
+          <t>336839</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>321312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144593</t>
+          <t>352407</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>583</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>220996</t>
+          <t>606771</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194613</t>
+          <t>583216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247288</t>
+          <t>627406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -2313,112 +2313,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>269931</t>
+          <t>96888</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>254412</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>283425</t>
+          <t>113638</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>336839</t>
+          <t>124108</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>321312</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>352407</t>
+          <t>144593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>606771</t>
+          <t>220996</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>583216</t>
+          <t>194613</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>627406</t>
+          <t>247288</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -2543,112 +2543,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50574</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>113131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62299</t>
+          <t>133462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>398</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>163746</t>
+          <t>431826</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144261</t>
+          <t>412809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187071</t>
+          <t>449872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>517</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>214320</t>
+          <t>556436</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189678</t>
+          <t>534169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>240674</t>
+          <t>576797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -2656,112 +2656,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>124610</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>113131</t>
+          <t>38922</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133462</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>431826</t>
+          <t>163746</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>412809</t>
+          <t>144261</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>449872</t>
+          <t>187071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>202</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>556436</t>
+          <t>214320</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>534169</t>
+          <t>189678</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>576797</t>
+          <t>240674</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -2886,112 +2886,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>546452</t>
+          <t>1382714</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507409</t>
+          <t>1345232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>588280</t>
+          <t>1417642</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>557351</t>
+          <t>1403727</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>515998</t>
+          <t>1371645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>597846</t>
+          <t>1438387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1103803</t>
+          <t>2786441</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1051174</t>
+          <t>2736150</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1164640</t>
+          <t>2835286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -2999,112 +2999,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>520</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1382714</t>
+          <t>546452</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1345232</t>
+          <t>507409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1417642</t>
+          <t>588280</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>535</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1403727</t>
+          <t>557351</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1371645</t>
+          <t>515998</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1438387</t>
+          <t>597846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2786441</t>
+          <t>1103803</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2736150</t>
+          <t>1051174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2835286</t>
+          <t>1164640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
